--- a/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_Auto.xlsx
+++ b/tests/vlaanderen/reference/resultaten/werk/concurrentie/inwoners/restdag/Ontpl_conc_Auto.xlsx
@@ -385,16 +385,16 @@
         <v>1</v>
       </c>
       <c r="B2">
-        <v>2.828655049581926</v>
+        <v>2.762471273708646</v>
       </c>
       <c r="C2">
-        <v>1.773799324762277</v>
+        <v>1.804986504150216</v>
       </c>
       <c r="D2">
-        <v>1.493186813606975</v>
+        <v>1.492356719727288</v>
       </c>
       <c r="E2">
-        <v>1.320195973509991</v>
+        <v>1.35008299623477</v>
       </c>
     </row>
     <row r="3" spans="1:5">
@@ -402,16 +402,16 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>2.883834815612765</v>
+        <v>2.716192778254065</v>
       </c>
       <c r="C3">
-        <v>1.790830877570517</v>
+        <v>1.777853943110417</v>
       </c>
       <c r="D3">
-        <v>1.500165029430641</v>
+        <v>1.488135239415128</v>
       </c>
       <c r="E3">
-        <v>1.325315907228028</v>
+        <v>1.349339608018896</v>
       </c>
     </row>
     <row r="4" spans="1:5">
@@ -419,16 +419,16 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>3.017320063453831</v>
+        <v>2.723795959846218</v>
       </c>
       <c r="C4">
-        <v>1.860444782376233</v>
+        <v>1.774452778225331</v>
       </c>
       <c r="D4">
-        <v>1.549274810175597</v>
+        <v>1.488447142412489</v>
       </c>
       <c r="E4">
-        <v>1.36634262392983</v>
+        <v>1.351006144102672</v>
       </c>
     </row>
     <row r="5" spans="1:5">
@@ -436,16 +436,16 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>3.380719459040115</v>
+        <v>2.859445027271143</v>
       </c>
       <c r="C5">
-        <v>1.998626836058858</v>
+        <v>1.846433052957773</v>
       </c>
       <c r="D5">
-        <v>1.601553576152952</v>
+        <v>1.518626883739414</v>
       </c>
       <c r="E5">
-        <v>1.409259220543114</v>
+        <v>1.382945653350103</v>
       </c>
     </row>
     <row r="6" spans="1:5">
@@ -453,16 +453,16 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>3.364883251118726</v>
+        <v>3.106889077795513</v>
       </c>
       <c r="C6">
-        <v>1.996492174193517</v>
+        <v>1.916531515436447</v>
       </c>
       <c r="D6">
-        <v>1.60245914882812</v>
+        <v>1.530706125062322</v>
       </c>
       <c r="E6">
-        <v>1.409908246290729</v>
+        <v>1.388846539973</v>
       </c>
     </row>
     <row r="7" spans="1:5">
@@ -470,16 +470,16 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>3.655791957161806</v>
+        <v>2.919700203054897</v>
       </c>
       <c r="C7">
-        <v>2.082638963899223</v>
+        <v>1.879362401327957</v>
       </c>
       <c r="D7">
-        <v>1.641837099424327</v>
+        <v>1.552962579133622</v>
       </c>
       <c r="E7">
-        <v>1.414435199910633</v>
+        <v>1.394664189341334</v>
       </c>
     </row>
     <row r="8" spans="1:5">
@@ -487,16 +487,16 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>1.617548854723349</v>
+        <v>2.722935837614904</v>
       </c>
       <c r="C8">
-        <v>1.331268593591207</v>
+        <v>1.683221729337924</v>
       </c>
       <c r="D8">
-        <v>1.25963316010294</v>
+        <v>1.418000201339182</v>
       </c>
       <c r="E8">
-        <v>1.286428854980599</v>
+        <v>1.311923632743135</v>
       </c>
     </row>
     <row r="9" spans="1:5">
@@ -504,16 +504,16 @@
         <v>8</v>
       </c>
       <c r="B9">
-        <v>3.031860211442694</v>
+        <v>2.676302776879262</v>
       </c>
       <c r="C9">
-        <v>1.862728241502912</v>
+        <v>1.757054191355407</v>
       </c>
       <c r="D9">
-        <v>1.549120835106843</v>
+        <v>1.484429531390895</v>
       </c>
       <c r="E9">
-        <v>1.366023141857575</v>
+        <v>1.350241973754367</v>
       </c>
     </row>
     <row r="10" spans="1:5">
@@ -521,16 +521,16 @@
         <v>9</v>
       </c>
       <c r="B10">
-        <v>3.67850446033196</v>
+        <v>2.807055806094718</v>
       </c>
       <c r="C10">
-        <v>2.084409928598445</v>
+        <v>1.842578070853054</v>
       </c>
       <c r="D10">
-        <v>1.639123914208649</v>
+        <v>1.532786781738554</v>
       </c>
       <c r="E10">
-        <v>1.409810408930863</v>
+        <v>1.376002053963837</v>
       </c>
     </row>
     <row r="11" spans="1:5">
@@ -538,16 +538,16 @@
         <v>10</v>
       </c>
       <c r="B11">
-        <v>3.781325438004659</v>
+        <v>2.869389087011561</v>
       </c>
       <c r="C11">
-        <v>2.106358068430189</v>
+        <v>1.860091254811437</v>
       </c>
       <c r="D11">
-        <v>1.646314611292481</v>
+        <v>1.5401080602619</v>
       </c>
       <c r="E11">
-        <v>1.414360880002127</v>
+        <v>1.382149816534359</v>
       </c>
     </row>
     <row r="12" spans="1:5">
@@ -555,16 +555,16 @@
         <v>11</v>
       </c>
       <c r="B12">
-        <v>3.573545316688636</v>
+        <v>2.668602923535555</v>
       </c>
       <c r="C12">
-        <v>2.058589535148216</v>
+        <v>1.802448729004363</v>
       </c>
       <c r="D12">
-        <v>1.6308334743146</v>
+        <v>1.520476970468435</v>
       </c>
       <c r="E12">
-        <v>1.405296775565356</v>
+        <v>1.368489245568724</v>
       </c>
     </row>
     <row r="13" spans="1:5">
@@ -572,16 +572,16 @@
         <v>12</v>
       </c>
       <c r="B13">
-        <v>3.657686037493024</v>
+        <v>2.779268884333532</v>
       </c>
       <c r="C13">
-        <v>2.079739547593902</v>
+        <v>1.833607780622675</v>
       </c>
       <c r="D13">
-        <v>1.636853583344017</v>
+        <v>1.528901761663319</v>
       </c>
       <c r="E13">
-        <v>1.408286739559427</v>
+        <v>1.373166809191563</v>
       </c>
     </row>
   </sheetData>
